--- a/tame_output/ON/bt/strategyON_20231203.xlsx
+++ b/tame_output/ON/bt/strategyON_20231203.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -41806,7 +41806,7 @@
         <v>45214</v>
       </c>
       <c r="B1752" t="n">
-        <v>2.81784116067579</v>
+        <v>2.817841160675789</v>
       </c>
       <c r="C1752" t="n">
         <v>2.953840430523644</v>
@@ -41829,7 +41829,7 @@
         <v>45215</v>
       </c>
       <c r="B1753" t="n">
-        <v>2.855808668290734</v>
+        <v>2.855808668290733</v>
       </c>
       <c r="C1753" t="n">
         <v>2.959094075792072</v>
@@ -41921,7 +41921,7 @@
         <v>45219</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.902669647939157</v>
+        <v>2.902669647939156</v>
       </c>
       <c r="C1757" t="n">
         <v>2.968547780644436</v>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947841</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968023</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42910,16 +42910,16 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>2.905710192189573</v>
+        <v>2.905710192189574</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>1.499321840606884</v>
+        <v>1.498607799473599</v>
       </c>
       <c r="E1800" t="n">
-        <v>3.682399466809312</v>
+        <v>3.682113850355998</v>
       </c>
       <c r="F1800" t="n">
         <v>2.092110092101119</v>

--- a/tame_output/ON/bt/strategyON_20231203.xlsx
+++ b/tame_output/ON/bt/strategyON_20231203.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -41806,7 +41806,7 @@
         <v>45214</v>
       </c>
       <c r="B1752" t="n">
-        <v>2.817841160675789</v>
+        <v>2.81784116067579</v>
       </c>
       <c r="C1752" t="n">
         <v>2.953840430523644</v>
@@ -41829,7 +41829,7 @@
         <v>45215</v>
       </c>
       <c r="B1753" t="n">
-        <v>2.855808668290733</v>
+        <v>2.855808668290734</v>
       </c>
       <c r="C1753" t="n">
         <v>2.959094075792072</v>
@@ -41921,7 +41921,7 @@
         <v>45219</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.902669647939156</v>
+        <v>2.902669647939157</v>
       </c>
       <c r="C1757" t="n">
         <v>2.968547780644436</v>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.91290325494784</v>
+        <v>2.912903254947841</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055149</v>
+        <v>3.04880620905515</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.05975199725568</v>
+        <v>3.059751997255681</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227614</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408316</v>
+        <v>3.069025022408317</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708495</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597767</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527686</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487811</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.14626574482338</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714842</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083875</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666732</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097097</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963478</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>1.498607799473599</v>
+        <v>1.499740017786276</v>
       </c>
       <c r="E1800" t="n">
-        <v>3.682113850355998</v>
+        <v>3.682566737681069</v>
       </c>
       <c r="F1800" t="n">
         <v>2.092110092101119</v>

--- a/tame_output/ON/bt/strategyON_20231203.xlsx
+++ b/tame_output/ON/bt/strategyON_20231203.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,35 +934,35 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2021-01-30</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-64.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.8%</t>
+          <t>451.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>-25.4%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1115,17 +1115,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,25 +1250,25 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1403,45 +1403,45 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2021-02-27</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -41674,16 +41674,16 @@
         <v>2.93174781975563</v>
       </c>
       <c r="D1746" t="n">
-        <v>1.277195935232383</v>
+        <v>0.9436242639772764</v>
       </c>
       <c r="E1746" t="n">
-        <v>3.442269769534836</v>
+        <v>3.308841101032793</v>
       </c>
       <c r="F1746" t="n">
-        <v>2.068336259439628</v>
+        <v>1.734764588184521</v>
       </c>
       <c r="G1746" t="n">
-        <v>4.172749575419409</v>
+        <v>3.972606572666344</v>
       </c>
     </row>
     <row r="1747">
@@ -41697,16 +41697,16 @@
         <v>2.933780970599019</v>
       </c>
       <c r="D1747" t="n">
-        <v>1.28168556371774</v>
+        <v>0.9481138924626334</v>
       </c>
       <c r="E1747" t="n">
-        <v>3.446098771772369</v>
+        <v>3.312670103270326</v>
       </c>
       <c r="F1747" t="n">
-        <v>2.072825887924985</v>
+        <v>1.739254216669878</v>
       </c>
       <c r="G1747" t="n">
-        <v>4.177476503354012</v>
+        <v>3.977333500600948</v>
       </c>
     </row>
     <row r="1748">
@@ -41720,16 +41720,16 @@
         <v>2.939301794739787</v>
       </c>
       <c r="D1748" t="n">
-        <v>1.282761076406529</v>
+        <v>0.9491894051514222</v>
       </c>
       <c r="E1748" t="n">
-        <v>3.452049800988652</v>
+        <v>3.31862113248661</v>
       </c>
       <c r="F1748" t="n">
-        <v>2.073901400613774</v>
+        <v>1.740329729358667</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.183642635108053</v>
+        <v>3.983499632354989</v>
       </c>
     </row>
     <row r="1749">
@@ -41743,16 +41743,16 @@
         <v>2.941291882277773</v>
       </c>
       <c r="D1749" t="n">
-        <v>1.280344013327877</v>
+        <v>0.9467723420727706</v>
       </c>
       <c r="E1749" t="n">
-        <v>3.453073063295177</v>
+        <v>3.319644394793134</v>
       </c>
       <c r="F1749" t="n">
-        <v>2.071484337535122</v>
+        <v>1.737912666280015</v>
       </c>
       <c r="G1749" t="n">
-        <v>4.184182484798848</v>
+        <v>3.984039482045784</v>
       </c>
     </row>
     <row r="1750">
@@ -41766,16 +41766,16 @@
         <v>2.950500122107244</v>
       </c>
       <c r="D1750" t="n">
-        <v>1.284392861345182</v>
+        <v>0.950821190090076</v>
       </c>
       <c r="E1750" t="n">
-        <v>3.46390084233157</v>
+        <v>3.330472173829528</v>
       </c>
       <c r="F1750" t="n">
-        <v>2.075533185552428</v>
+        <v>1.741961514297321</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.195820033438703</v>
+        <v>3.995677030685639</v>
       </c>
     </row>
     <row r="1751">
@@ -41789,16 +41789,16 @@
         <v>2.950191610492619</v>
       </c>
       <c r="D1751" t="n">
-        <v>1.284027150304152</v>
+        <v>0.9504554790490451</v>
       </c>
       <c r="E1751" t="n">
-        <v>3.463446046300533</v>
+        <v>3.33001737779849</v>
       </c>
       <c r="F1751" t="n">
-        <v>2.074662691335144</v>
+        <v>1.741091020080037</v>
       </c>
       <c r="G1751" t="n">
-        <v>4.194989225293708</v>
+        <v>3.994846222540644</v>
       </c>
     </row>
     <row r="1752">
@@ -41812,16 +41812,16 @@
         <v>2.953840430523644</v>
       </c>
       <c r="D1752" t="n">
-        <v>1.283653737293151</v>
+        <v>0.9500820660380445</v>
       </c>
       <c r="E1752" t="n">
-        <v>3.466945501127157</v>
+        <v>3.333516832625115</v>
       </c>
       <c r="F1752" t="n">
-        <v>2.074662691335144</v>
+        <v>1.741091020080037</v>
       </c>
       <c r="G1752" t="n">
-        <v>4.198638045324732</v>
+        <v>3.998495042571668</v>
       </c>
     </row>
     <row r="1753">
@@ -41835,16 +41835,16 @@
         <v>2.959094075792072</v>
       </c>
       <c r="D1753" t="n">
-        <v>1.289164681759864</v>
+        <v>0.955593010504758</v>
       </c>
       <c r="E1753" t="n">
-        <v>3.474403524182271</v>
+        <v>3.340974855680228</v>
       </c>
       <c r="F1753" t="n">
-        <v>2.074662691335144</v>
+        <v>1.741091020080037</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.20389169059316</v>
+        <v>4.003748687840095</v>
       </c>
     </row>
     <row r="1754">
@@ -41858,16 +41858,16 @@
         <v>2.957874679524909</v>
       </c>
       <c r="D1754" t="n">
-        <v>1.28943525910119</v>
+        <v>0.9558635878460838</v>
       </c>
       <c r="E1754" t="n">
-        <v>3.473292358851638</v>
+        <v>3.339863690349596</v>
       </c>
       <c r="F1754" t="n">
-        <v>2.075159217637795</v>
+        <v>1.741587546382688</v>
       </c>
       <c r="G1754" t="n">
-        <v>4.202970210107588</v>
+        <v>4.002827207354523</v>
       </c>
     </row>
     <row r="1755">
@@ -41881,16 +41881,16 @@
         <v>2.95420083304114</v>
       </c>
       <c r="D1755" t="n">
-        <v>1.297420427482935</v>
+        <v>0.9638487562278283</v>
       </c>
       <c r="E1755" t="n">
-        <v>3.472812579720567</v>
+        <v>3.339383911218525</v>
       </c>
       <c r="F1755" t="n">
-        <v>2.077386763674572</v>
+        <v>1.743815092419465</v>
       </c>
       <c r="G1755" t="n">
-        <v>4.200632891245885</v>
+        <v>4.000489888492821</v>
       </c>
     </row>
     <row r="1756">
@@ -41904,16 +41904,16 @@
         <v>2.969006534107256</v>
       </c>
       <c r="D1756" t="n">
-        <v>1.286534063711891</v>
+        <v>0.9529623924567846</v>
       </c>
       <c r="E1756" t="n">
-        <v>3.483263735278265</v>
+        <v>3.349835066776223</v>
       </c>
       <c r="F1756" t="n">
-        <v>2.077386763674572</v>
+        <v>1.743815092419465</v>
       </c>
       <c r="G1756" t="n">
-        <v>4.215438592312001</v>
+        <v>4.015295589558936</v>
       </c>
     </row>
     <row r="1757">
@@ -41921,22 +41921,22 @@
         <v>45219</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.902669647939157</v>
+        <v>2.902669647939156</v>
       </c>
       <c r="C1757" t="n">
         <v>2.968547780644436</v>
       </c>
       <c r="D1757" t="n">
-        <v>1.294651203669536</v>
+        <v>0.9610795324144298</v>
       </c>
       <c r="E1757" t="n">
-        <v>3.486051837798504</v>
+        <v>3.352623169296461</v>
       </c>
       <c r="F1757" t="n">
-        <v>2.077386763674572</v>
+        <v>1.743815092419465</v>
       </c>
       <c r="G1757" t="n">
-        <v>4.214979838849181</v>
+        <v>4.014836836096117</v>
       </c>
     </row>
     <row r="1758">
@@ -41944,22 +41944,22 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947841</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
       </c>
       <c r="D1758" t="n">
-        <v>1.299160551895321</v>
+        <v>0.965588880640215</v>
       </c>
       <c r="E1758" t="n">
-        <v>3.484454661719184</v>
+        <v>3.351025993217141</v>
       </c>
       <c r="F1758" t="n">
-        <v>2.077386763674572</v>
+        <v>1.743815092419465</v>
       </c>
       <c r="G1758" t="n">
-        <v>4.211578923479547</v>
+        <v>4.011435920726483</v>
       </c>
     </row>
     <row r="1759">
@@ -41973,16 +41973,16 @@
         <v>2.964689051375926</v>
       </c>
       <c r="D1759" t="n">
-        <v>1.288853426237886</v>
+        <v>0.9552817549827799</v>
       </c>
       <c r="E1759" t="n">
-        <v>3.479873997557334</v>
+        <v>3.346445329055291</v>
       </c>
       <c r="F1759" t="n">
-        <v>2.070388381359718</v>
+        <v>1.736816710104611</v>
       </c>
       <c r="G1759" t="n">
-        <v>4.206922080191759</v>
+        <v>4.006779077438694</v>
       </c>
     </row>
     <row r="1760">
@@ -41996,16 +41996,16 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>1.240610777352174</v>
+        <v>0.9070391060970679</v>
       </c>
       <c r="E1760" t="n">
-        <v>3.488362595961227</v>
+        <v>3.354933927459185</v>
       </c>
       <c r="F1760" t="n">
-        <v>2.070388381359718</v>
+        <v>1.736816710104611</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.234707738149936</v>
+        <v>4.034564735396873</v>
       </c>
     </row>
     <row r="1761">
@@ -42019,16 +42019,16 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>1.247708778319676</v>
+        <v>0.9141371070645696</v>
       </c>
       <c r="E1761" t="n">
-        <v>3.508976505389688</v>
+        <v>3.375547836887645</v>
       </c>
       <c r="F1761" t="n">
-        <v>2.070495579471094</v>
+        <v>1.736923908215987</v>
       </c>
       <c r="G1761" t="n">
-        <v>4.252546766058222</v>
+        <v>4.052403763305158</v>
       </c>
     </row>
     <row r="1762">
@@ -42042,16 +42042,16 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>1.248911844615782</v>
+        <v>0.9153401733606761</v>
       </c>
       <c r="E1762" t="n">
-        <v>3.50993129158917</v>
+        <v>3.376502623087128</v>
       </c>
       <c r="F1762" t="n">
-        <v>2.070495579471094</v>
+        <v>1.736923908215987</v>
       </c>
       <c r="G1762" t="n">
-        <v>4.253020325739262</v>
+        <v>4.052877322986198</v>
       </c>
     </row>
     <row r="1763">
@@ -42065,16 +42065,16 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>1.251264891949028</v>
+        <v>0.9176932206939216</v>
       </c>
       <c r="E1763" t="n">
-        <v>3.516211882659366</v>
+        <v>3.382783214157323</v>
       </c>
       <c r="F1763" t="n">
-        <v>2.07284862680434</v>
+        <v>1.739276955549232</v>
       </c>
       <c r="G1763" t="n">
-        <v>4.259771526276107</v>
+        <v>4.059628523523043</v>
       </c>
     </row>
     <row r="1764">
@@ -42088,16 +42088,16 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>1.252381173940254</v>
+        <v>0.9188095026851477</v>
       </c>
       <c r="E1764" t="n">
-        <v>3.531235420291906</v>
+        <v>3.397806751789864</v>
       </c>
       <c r="F1764" t="n">
-        <v>2.073964908795566</v>
+        <v>1.740393237540458</v>
       </c>
       <c r="G1764" t="n">
-        <v>4.275018320306892</v>
+        <v>4.074875317553828</v>
       </c>
     </row>
     <row r="1765">
@@ -42111,16 +42111,16 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>1.256119130001309</v>
+        <v>0.9225474587462031</v>
       </c>
       <c r="E1765" t="n">
-        <v>3.532655583579975</v>
+        <v>3.399226915077933</v>
       </c>
       <c r="F1765" t="n">
-        <v>2.07634136107619</v>
+        <v>1.742769689821083</v>
       </c>
       <c r="G1765" t="n">
-        <v>4.276369172538915</v>
+        <v>4.07622616978585</v>
       </c>
     </row>
     <row r="1766">
@@ -42134,16 +42134,16 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>1.264616275662442</v>
+        <v>0.9310446044073364</v>
       </c>
       <c r="E1766" t="n">
-        <v>3.534369866342523</v>
+        <v>3.40094119784048</v>
       </c>
       <c r="F1766" t="n">
-        <v>2.07634136107619</v>
+        <v>1.742769689821083</v>
       </c>
       <c r="G1766" t="n">
-        <v>4.274684597037009</v>
+        <v>4.074541594283945</v>
       </c>
     </row>
     <row r="1767">
@@ -42157,16 +42157,16 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>1.264924235747167</v>
+        <v>0.9313525644920611</v>
       </c>
       <c r="E1767" t="n">
-        <v>3.538881626057259</v>
+        <v>3.405452957555216</v>
       </c>
       <c r="F1767" t="n">
-        <v>2.07752307516889</v>
+        <v>1.743951403913783</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.279782201173475</v>
+        <v>4.07963919842041</v>
       </c>
     </row>
     <row r="1768">
@@ -42174,22 +42174,22 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>1.266705998117758</v>
+        <v>0.9331343268626524</v>
       </c>
       <c r="E1768" t="n">
-        <v>3.54125462818237</v>
+        <v>3.407825959680328</v>
       </c>
       <c r="F1768" t="n">
-        <v>2.07752307516889</v>
+        <v>1.743951403913783</v>
       </c>
       <c r="G1768" t="n">
-        <v>4.28144249835035</v>
+        <v>4.081299495597285</v>
       </c>
     </row>
     <row r="1769">
@@ -42197,22 +42197,22 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>1.262628642980667</v>
+        <v>0.929056971725561</v>
       </c>
       <c r="E1769" t="n">
-        <v>3.554657856391223</v>
+        <v>3.421229187889181</v>
       </c>
       <c r="F1769" t="n">
-        <v>2.07752307516889</v>
+        <v>1.743951403913783</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.29647666861404</v>
+        <v>4.096333665860976</v>
       </c>
     </row>
     <row r="1770">
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>1.272620723907076</v>
+        <v>0.9390490526519701</v>
       </c>
       <c r="E1770" t="n">
-        <v>3.556969123425921</v>
+        <v>3.423540454923878</v>
       </c>
       <c r="F1770" t="n">
-        <v>2.0875151560953</v>
+        <v>1.753943484840192</v>
       </c>
       <c r="G1770" t="n">
-        <v>4.300786351834018</v>
+        <v>4.100643349080954</v>
       </c>
     </row>
     <row r="1771">
@@ -42243,22 +42243,22 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>1.272064968851038</v>
+        <v>0.9384932975959324</v>
       </c>
       <c r="E1771" t="n">
-        <v>3.559648631300096</v>
+        <v>3.426219962798054</v>
       </c>
       <c r="F1771" t="n">
-        <v>2.085907742334222</v>
+        <v>1.752336071079114</v>
       </c>
       <c r="G1771" t="n">
-        <v>4.302723713473963</v>
+        <v>4.102580710720899</v>
       </c>
     </row>
     <row r="1772">
@@ -42266,22 +42266,22 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>1.268850616437727</v>
+        <v>0.9352789451826209</v>
       </c>
       <c r="E1772" t="n">
-        <v>3.563887879473919</v>
+        <v>3.430459210971877</v>
       </c>
       <c r="F1772" t="n">
-        <v>2.085907742334222</v>
+        <v>1.752336071079114</v>
       </c>
       <c r="G1772" t="n">
-        <v>4.30824870261311</v>
+        <v>4.108105699860046</v>
       </c>
     </row>
     <row r="1773">
@@ -42289,22 +42289,22 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968024</v>
+        <v>3.073923642968023</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>1.251842371035117</v>
+        <v>0.9182706997800114</v>
       </c>
       <c r="E1773" t="n">
-        <v>3.558162153950607</v>
+        <v>3.424733485448564</v>
       </c>
       <c r="F1773" t="n">
-        <v>2.088906877347195</v>
+        <v>1.755335206092088</v>
       </c>
       <c r="G1773" t="n">
-        <v>4.311125756258625</v>
+        <v>4.110982753505561</v>
       </c>
     </row>
     <row r="1774">
@@ -42312,22 +42312,22 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>1.270802093486472</v>
+        <v>0.937230422231366</v>
       </c>
       <c r="E1774" t="n">
-        <v>3.566495905102421</v>
+        <v>3.433067236600379</v>
       </c>
       <c r="F1774" t="n">
-        <v>2.088906877347195</v>
+        <v>1.755335206092088</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.311875618429898</v>
+        <v>4.111732615676834</v>
       </c>
     </row>
     <row r="1775">
@@ -42335,22 +42335,22 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>1.272036818089281</v>
+        <v>0.9384651468341747</v>
       </c>
       <c r="E1775" t="n">
-        <v>3.565225392407126</v>
+        <v>3.431796723905083</v>
       </c>
       <c r="F1775" t="n">
-        <v>2.088906877347195</v>
+        <v>1.755335206092088</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.310111215893479</v>
+        <v>4.109968213140415</v>
       </c>
     </row>
     <row r="1776">
@@ -42358,22 +42358,22 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>1.262002554265632</v>
+        <v>0.928430883010526</v>
       </c>
       <c r="E1776" t="n">
-        <v>3.564779296714528</v>
+        <v>3.431350628212486</v>
       </c>
       <c r="F1776" t="n">
-        <v>2.088906877347195</v>
+        <v>1.755335206092088</v>
       </c>
       <c r="G1776" t="n">
-        <v>4.313678825730341</v>
+        <v>4.113535822977277</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>1.256963555967765</v>
+        <v>0.9233918847126592</v>
       </c>
       <c r="E1777" t="n">
-        <v>3.58674565928499</v>
+        <v>3.453316990782948</v>
       </c>
       <c r="F1777" t="n">
-        <v>2.083867879049329</v>
+        <v>1.750296207794222</v>
       </c>
       <c r="G1777" t="n">
-        <v>4.33463738864123</v>
+        <v>4.134494385888166</v>
       </c>
     </row>
     <row r="1778">
@@ -42404,22 +42404,22 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>1.266783274128316</v>
+        <v>0.9332116028732099</v>
       </c>
       <c r="E1778" t="n">
-        <v>3.58814225803644</v>
+        <v>3.454713589534398</v>
       </c>
       <c r="F1778" t="n">
-        <v>2.090297819266016</v>
+        <v>1.756726148010909</v>
       </c>
       <c r="G1778" t="n">
-        <v>4.335964064258472</v>
+        <v>4.135821061505408</v>
       </c>
     </row>
     <row r="1779">
@@ -42427,22 +42427,22 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>1.26858490096727</v>
+        <v>0.9350132297121638</v>
       </c>
       <c r="E1779" t="n">
-        <v>3.574111470775648</v>
+        <v>3.440682802273605</v>
       </c>
       <c r="F1779" t="n">
-        <v>2.090297819266016</v>
+        <v>1.756726148010909</v>
       </c>
       <c r="G1779" t="n">
-        <v>4.321212626262097</v>
+        <v>4.121069623509034</v>
       </c>
     </row>
     <row r="1780">
@@ -42450,22 +42450,22 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>1.269573582711438</v>
+        <v>0.9360019114563316</v>
       </c>
       <c r="E1780" t="n">
-        <v>3.572620699788987</v>
+        <v>3.439192031286944</v>
       </c>
       <c r="F1780" t="n">
-        <v>2.090297819266016</v>
+        <v>1.756726148010909</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.31932638257777</v>
+        <v>4.119183379824706</v>
       </c>
     </row>
     <row r="1781">
@@ -42473,22 +42473,22 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>1.277569937232977</v>
+        <v>0.9439982659778702</v>
       </c>
       <c r="E1781" t="n">
-        <v>3.577792868053443</v>
+        <v>3.4443641995514</v>
       </c>
       <c r="F1781" t="n">
-        <v>2.098294173787555</v>
+        <v>1.764722502532448</v>
       </c>
       <c r="G1781" t="n">
-        <v>4.326097821746534</v>
+        <v>4.125954818993469</v>
       </c>
     </row>
     <row r="1782">
@@ -42496,22 +42496,22 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>1.282553687904885</v>
+        <v>0.9489820166497789</v>
       </c>
       <c r="E1782" t="n">
-        <v>3.591624948913118</v>
+        <v>3.458196280411075</v>
       </c>
       <c r="F1782" t="n">
-        <v>2.103277924459463</v>
+        <v>1.769706253204356</v>
       </c>
       <c r="G1782" t="n">
-        <v>4.34092665274059</v>
+        <v>4.140783649987526</v>
       </c>
     </row>
     <row r="1783">
@@ -42519,22 +42519,22 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>1.288939826854441</v>
+        <v>0.9553681555993344</v>
       </c>
       <c r="E1783" t="n">
-        <v>3.600907607504729</v>
+        <v>3.467478939002687</v>
       </c>
       <c r="F1783" t="n">
-        <v>2.103277924459463</v>
+        <v>1.769706253204356</v>
       </c>
       <c r="G1783" t="n">
-        <v>4.34765485575238</v>
+        <v>4.147511852999315</v>
       </c>
     </row>
     <row r="1784">
@@ -42542,22 +42542,22 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>1.277134476535808</v>
+        <v>0.9435628052807018</v>
       </c>
       <c r="E1784" t="n">
-        <v>3.600201556136819</v>
+        <v>3.466772887634776</v>
       </c>
       <c r="F1784" t="n">
-        <v>2.091472574140831</v>
+        <v>1.757900902885724</v>
       </c>
       <c r="G1784" t="n">
-        <v>4.344587734320743</v>
+        <v>4.144444731567678</v>
       </c>
     </row>
     <row r="1785">
@@ -42565,22 +42565,22 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>1.285866287314474</v>
+        <v>0.952294616059368</v>
       </c>
       <c r="E1785" t="n">
-        <v>3.609641738058174</v>
+        <v>3.476213069556132</v>
       </c>
       <c r="F1785" t="n">
-        <v>2.100204384919497</v>
+        <v>1.76663271366439</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.355774278397831</v>
+        <v>4.155631275644767</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>1.292203173958926</v>
+        <v>0.95863150270382</v>
       </c>
       <c r="E1786" t="n">
-        <v>3.607487311663941</v>
+        <v>3.474058643161898</v>
       </c>
       <c r="F1786" t="n">
-        <v>2.100204384919497</v>
+        <v>1.76663271366439</v>
       </c>
       <c r="G1786" t="n">
-        <v>4.351085097345817</v>
+        <v>4.150942094592753</v>
       </c>
     </row>
     <row r="1787">
@@ -42611,22 +42611,22 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>1.294737621686295</v>
+        <v>0.9611659504311884</v>
       </c>
       <c r="E1787" t="n">
-        <v>3.618463748557082</v>
+        <v>3.485035080055039</v>
       </c>
       <c r="F1787" t="n">
-        <v>2.100204384919497</v>
+        <v>1.76663271366439</v>
       </c>
       <c r="G1787" t="n">
-        <v>4.361047755148011</v>
+        <v>4.160904752394946</v>
       </c>
     </row>
     <row r="1788">
@@ -42634,22 +42634,22 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>1.29466172270569</v>
+        <v>0.9610900514505838</v>
       </c>
       <c r="E1788" t="n">
-        <v>3.61084806915775</v>
+        <v>3.477419400655707</v>
       </c>
       <c r="F1788" t="n">
-        <v>2.100967645608824</v>
+        <v>1.767395974353717</v>
       </c>
       <c r="G1788" t="n">
-        <v>4.353920391754516</v>
+        <v>4.153777389001452</v>
       </c>
     </row>
     <row r="1789">
@@ -42657,22 +42657,22 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>1.284159533146344</v>
+        <v>0.9505878618912371</v>
       </c>
       <c r="E1789" t="n">
-        <v>3.584411769124384</v>
+        <v>3.450983100622342</v>
       </c>
       <c r="F1789" t="n">
-        <v>2.090465456049478</v>
+        <v>1.75689378479437</v>
       </c>
       <c r="G1789" t="n">
-        <v>4.325383653809282</v>
+        <v>4.125240651056218</v>
       </c>
     </row>
     <row r="1790">
@@ -42680,22 +42680,22 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>1.282326270467227</v>
+        <v>0.9487545992121208</v>
       </c>
       <c r="E1790" t="n">
-        <v>3.58437930389886</v>
+        <v>3.450950635396817</v>
       </c>
       <c r="F1790" t="n">
-        <v>2.090465456049478</v>
+        <v>1.75689378479437</v>
       </c>
       <c r="G1790" t="n">
-        <v>4.326084493655403</v>
+        <v>4.125941490902339</v>
       </c>
     </row>
     <row r="1791">
@@ -42703,22 +42703,22 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>1.277317155405643</v>
+        <v>0.9437454841505368</v>
       </c>
       <c r="E1791" t="n">
-        <v>3.582892737703085</v>
+        <v>3.449464069201043</v>
       </c>
       <c r="F1791" t="n">
-        <v>2.089470878490943</v>
+        <v>1.755899207235835</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.326004826949142</v>
+        <v>4.125861824196078</v>
       </c>
     </row>
     <row r="1792">
@@ -42726,22 +42726,22 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>1.273611598768829</v>
+        <v>0.9400399275137222</v>
       </c>
       <c r="E1792" t="n">
-        <v>3.580638240288725</v>
+        <v>3.447209571786682</v>
       </c>
       <c r="F1792" t="n">
-        <v>2.087601203233308</v>
+        <v>1.754029531978201</v>
       </c>
       <c r="G1792" t="n">
-        <v>4.324110747034926</v>
+        <v>4.123967744281862</v>
       </c>
     </row>
     <row r="1793">
@@ -42749,22 +42749,22 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>1.274843924126194</v>
+        <v>0.9412722528710877</v>
       </c>
       <c r="E1793" t="n">
-        <v>3.58155102249399</v>
+        <v>3.448122353991948</v>
       </c>
       <c r="F1793" t="n">
-        <v>2.088231579605346</v>
+        <v>1.754659908350238</v>
       </c>
       <c r="G1793" t="n">
-        <v>4.324908824920469</v>
+        <v>4.124765822167404</v>
       </c>
     </row>
     <row r="1794">
@@ -42772,22 +42772,22 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>1.285171921142046</v>
+        <v>0.9516002498869399</v>
       </c>
       <c r="E1794" t="n">
-        <v>3.589812129464545</v>
+        <v>3.456383460962502</v>
       </c>
       <c r="F1794" t="n">
-        <v>2.098559576621198</v>
+        <v>1.764987905366091</v>
       </c>
       <c r="G1794" t="n">
-        <v>4.335235531294193</v>
+        <v>4.135092528541128</v>
       </c>
     </row>
     <row r="1795">
@@ -42795,22 +42795,22 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083875</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>1.285288256289602</v>
+        <v>0.9517165850344956</v>
       </c>
       <c r="E1795" t="n">
-        <v>3.596379323725403</v>
+        <v>3.462950655223361</v>
       </c>
       <c r="F1795" t="n">
-        <v>2.098675911768754</v>
+        <v>1.765104240513646</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.341825992584563</v>
+        <v>4.141682989831499</v>
       </c>
     </row>
     <row r="1796">
@@ -42818,22 +42818,22 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666732</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>1.283442846712735</v>
+        <v>0.9498711754576281</v>
       </c>
       <c r="E1796" t="n">
-        <v>3.592615130340045</v>
+        <v>3.459186461838002</v>
       </c>
       <c r="F1796" t="n">
-        <v>2.098675911768754</v>
+        <v>1.765104240513646</v>
       </c>
       <c r="G1796" t="n">
-        <v>4.338799963029952</v>
+        <v>4.138656960276887</v>
       </c>
     </row>
     <row r="1797">
@@ -42841,22 +42841,22 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097097</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>1.284941279237833</v>
+        <v>0.951369607982727</v>
       </c>
       <c r="E1797" t="n">
-        <v>3.593152791211218</v>
+        <v>3.459724122709175</v>
       </c>
       <c r="F1797" t="n">
-        <v>2.100174344293853</v>
+        <v>1.766602673038745</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.339637310406145</v>
+        <v>4.13949430765308</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>1.2768770270451</v>
+        <v>0.9433053557899931</v>
       </c>
       <c r="E1798" t="n">
-        <v>3.591205068277436</v>
+        <v>3.457776399775393</v>
       </c>
       <c r="F1798" t="n">
-        <v>2.092110092101119</v>
+        <v>1.758538420846011</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.336076737033816</v>
+        <v>4.135933734280751</v>
       </c>
     </row>
     <row r="1799">
@@ -42887,22 +42887,22 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.185514355963478</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>1.275547059583887</v>
+        <v>0.9419753883287807</v>
       </c>
       <c r="E1799" t="n">
-        <v>3.590673081292951</v>
+        <v>3.457244412790908</v>
       </c>
       <c r="F1799" t="n">
-        <v>2.092110092101119</v>
+        <v>1.758538420846011</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.336076737033816</v>
+        <v>4.135933734280751</v>
       </c>
     </row>
     <row r="1800">
@@ -42910,22 +42910,22 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>2.905710192189574</v>
+        <v>2.896267444402778</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>1.499740017786276</v>
+        <v>1.169840071062292</v>
       </c>
       <c r="E1800" t="n">
-        <v>3.682566737681069</v>
+        <v>3.550606758991475</v>
       </c>
       <c r="F1800" t="n">
-        <v>2.092110092101119</v>
+        <v>1.758538420846011</v>
       </c>
       <c r="G1800" t="n">
-        <v>4.338293210140978</v>
+        <v>4.138150207387914</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231203.xlsx
+++ b/tame_output/ON/bt/strategyON_20231203.xlsx
@@ -41806,7 +41806,7 @@
         <v>45214</v>
       </c>
       <c r="B1752" t="n">
-        <v>2.81784116067579</v>
+        <v>2.817841160675789</v>
       </c>
       <c r="C1752" t="n">
         <v>2.953840430523644</v>
@@ -41829,7 +41829,7 @@
         <v>45215</v>
       </c>
       <c r="B1753" t="n">
-        <v>2.855808668290734</v>
+        <v>2.855808668290733</v>
       </c>
       <c r="C1753" t="n">
         <v>2.959094075792072</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.04880620905515</v>
+        <v>3.048806209055149</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968023</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
